--- a/DRIVE/3. Operações/3.1 Projetos/26002 - SS AEISEP (Porto)/Peças escritas/ORÇAMENTO V_FINAL POR-2026-0002-SSYS.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/26002 - SS AEISEP (Porto)/Peças escritas/ORÇAMENTO V_FINAL POR-2026-0002-SSYS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\26002 - SS AEISEP (Porto)\Peças escritas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4BEF21-C347-4FEE-AF67-6AE9A6463C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B53B9B-3485-4DF4-BB53-42D4D9E6B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -629,6 +629,9 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -661,9 +664,6 @@
     </xf>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -998,11 +998,11 @@
       <c r="A2" s="35"/>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
       <c r="G2" s="37"/>
     </row>
     <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,7 +1112,7 @@
     </row>
     <row r="11" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="61">
+      <c r="B11" s="62">
         <v>1</v>
       </c>
       <c r="C11" s="52"/>
@@ -1123,20 +1123,20 @@
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="61"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="53" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="54"/>
-      <c r="E12" s="66" t="s">
+      <c r="E12" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="67"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="62"/>
+      <c r="B13" s="63"/>
       <c r="C13" s="34" t="s">
         <v>28</v>
       </c>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="14" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="63">
+      <c r="B14" s="64">
         <v>2</v>
       </c>
       <c r="C14" s="9"/>
@@ -1158,27 +1158,27 @@
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="64"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="7">
-        <f>101*1.3</f>
-        <v>131.30000000000001</v>
+        <f>101*1.33665</f>
+        <v>135.00164999999998</v>
       </c>
       <c r="E15" s="8">
         <f>D15*B14</f>
-        <v>262.60000000000002</v>
+        <v>270.00329999999997</v>
       </c>
       <c r="F15" s="13">
         <f>E15</f>
-        <v>262.60000000000002</v>
+        <v>270.00329999999997</v>
       </c>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="65"/>
+      <c r="B16" s="66"/>
       <c r="C16" s="34" t="s">
         <v>18</v>
       </c>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="17" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="63">
+      <c r="B17" s="64">
         <v>1</v>
       </c>
       <c r="C17" s="9"/>
@@ -1200,27 +1200,27 @@
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="64"/>
+      <c r="B18" s="65"/>
       <c r="C18" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="7">
-        <f>126*1.3</f>
-        <v>163.80000000000001</v>
+        <f>126*1.26985</f>
+        <v>160.00109999999998</v>
       </c>
       <c r="E18" s="8">
         <f>D18*B17</f>
-        <v>163.80000000000001</v>
+        <v>160.00109999999998</v>
       </c>
       <c r="F18" s="13">
         <f>E18</f>
-        <v>163.80000000000001</v>
+        <v>160.00109999999998</v>
       </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="65"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="34" t="s">
         <v>20</v>
       </c>
@@ -1231,7 +1231,7 @@
     </row>
     <row r="20" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="63">
+      <c r="B20" s="64">
         <v>4</v>
       </c>
       <c r="C20" s="9"/>
@@ -1242,27 +1242,26 @@
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="64"/>
+      <c r="B21" s="65"/>
       <c r="C21" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="7">
-        <f>48*1.3</f>
-        <v>62.400000000000006</v>
+        <f>48.386556*1.291655</f>
+        <v>62.498736990179999</v>
       </c>
       <c r="E21" s="8">
-        <f>B20*D21</f>
-        <v>249.60000000000002</v>
+        <v>250</v>
       </c>
       <c r="F21" s="13">
         <f>E21</f>
-        <v>249.60000000000002</v>
+        <v>250</v>
       </c>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="65"/>
+      <c r="B22" s="66"/>
       <c r="C22" s="34" t="s">
         <v>22</v>
       </c>
@@ -1273,7 +1272,7 @@
     </row>
     <row r="23" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="63">
+      <c r="B23" s="64">
         <v>1</v>
       </c>
       <c r="C23" s="9"/>
@@ -1284,7 +1283,7 @@
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="64"/>
+      <c r="B24" s="65"/>
       <c r="C24" s="56" t="s">
         <v>31</v>
       </c>
@@ -1303,7 +1302,7 @@
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="65"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="34" t="s">
         <v>30</v>
       </c>
@@ -1454,7 +1453,7 @@
       <c r="E58" s="44"/>
       <c r="F58" s="45">
         <f>SUM(F12,F15,F18,F24,F21)</f>
-        <v>766.00000000000011</v>
+        <v>770.00439999999992</v>
       </c>
       <c r="G58" s="46"/>
     </row>
@@ -1463,15 +1462,15 @@
       <c r="G59" s="2"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="59"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="60"/>
     </row>
     <row r="61" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="31"/>
@@ -1488,11 +1487,11 @@
         <v>5</v>
       </c>
       <c r="C62" s="49"/>
-      <c r="D62" s="60" t="s">
+      <c r="D62" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="60"/>
-      <c r="F62" s="60"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
       <c r="G62" s="50"/>
     </row>
   </sheetData>

--- a/DRIVE/3. Operações/3.1 Projetos/26002 - SS AEISEP (Porto)/Peças escritas/ORÇAMENTO V_FINAL POR-2026-0002-SSYS.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/26002 - SS AEISEP (Porto)/Peças escritas/ORÇAMENTO V_FINAL POR-2026-0002-SSYS.xlsx
@@ -5,20 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\26002 - SS AEISEP (Porto)\Peças escritas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruisa\mind7\MINDSET\DRIVE\3. Operações\3.1 Projetos\26002 - SS AEISEP (Porto)\Peças escritas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B53B9B-3485-4DF4-BB53-42D4D9E6B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE2E051-E799-4A3E-BA44-A8DB54748D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Proposta" sheetId="1" r:id="rId1"/>
+    <sheet name="PROJETO DE AUDIO" sheetId="1" r:id="rId1"/>
+    <sheet name="IVA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Proposta!$A$1:$G$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PROJETO DE AUDIO'!$A$1:$G$61</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>DESIGNAÇÃO / DESCRIÇÃO</t>
   </si>
@@ -50,9 +51,6 @@
     <t>SUB-TOTAL (€)</t>
   </si>
   <si>
-    <t>TOTAL (€)</t>
-  </si>
-  <si>
     <t>AE ISEP</t>
   </si>
   <si>
@@ -89,9 +87,6 @@
     <t>PAGINAS</t>
   </si>
   <si>
-    <t>Audibax 1202 FX USB</t>
-  </si>
-  <si>
     <t>Audibax Arkansas 8</t>
   </si>
   <si>
@@ -113,9 +108,6 @@
     <t>TOTAL S/ IVA</t>
   </si>
   <si>
-    <t>NOTAS: Portes de envio a decidir. Preços por unidade apresentados não incluem IVA.Orçamento sujeito a revisões.</t>
-  </si>
-  <si>
     <t>Pré-pagamento</t>
   </si>
   <si>
@@ -125,9 +117,6 @@
     <t>A encomendar pelo cliente</t>
   </si>
   <si>
-    <t>Mesa de mistura 18 canais profissional (6 mic + 4 estéreo + USB)</t>
-  </si>
-  <si>
     <t>PROJETO DE AUDIO C/ INSTALAÇÃO E MANUTENÇÃO</t>
   </si>
   <si>
@@ -140,17 +129,85 @@
     <t>2º</t>
   </si>
   <si>
-    <t>Dependente do fornecedor</t>
+    <t xml:space="preserve">Behringer Xenyx </t>
+  </si>
+  <si>
+    <t>X1832USB</t>
+  </si>
+  <si>
+    <t>PORTE DE ENVIO</t>
+  </si>
+  <si>
+    <t>NOTAS: Preços por unidade apresentados não incluem IVA.Orçamento sujeito a revisões.</t>
+  </si>
+  <si>
+    <t>1/2 semanas (desde o dia da aprovação)</t>
+  </si>
+  <si>
+    <t>Acessórios de montagem</t>
+  </si>
+  <si>
+    <t>Abraçadeiras de aluminio/plástico, Fita Fita Termo Retratil, etc.</t>
+  </si>
+  <si>
+    <t>DISCRIMINAÇÃO DE IVA</t>
+  </si>
+  <si>
+    <t>Taxa IVA:</t>
+  </si>
+  <si>
+    <t>QTD</t>
+  </si>
+  <si>
+    <t>DESIGNAÇÃO</t>
+  </si>
+  <si>
+    <t>PREÇO/UN S/IVA (€)</t>
+  </si>
+  <si>
+    <t>SUB-TOTAL S/IVA (€)</t>
+  </si>
+  <si>
+    <t>IVA (€)</t>
+  </si>
+  <si>
+    <t>TOTAL C/IVA (€)</t>
+  </si>
+  <si>
+    <t>Portes de envio</t>
+  </si>
+  <si>
+    <t>TOTAIS</t>
+  </si>
+  <si>
+    <t>Total S/IVA:</t>
+  </si>
+  <si>
+    <t>Total IVA:</t>
+  </si>
+  <si>
+    <t>Total C/IVA:</t>
+  </si>
+  <si>
+    <t>TOTAL c/IVA (€)</t>
+  </si>
+  <si>
+    <t>luis c iva</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
+    <numFmt numFmtId="166" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00\ \€;\(#,##0.00\ \€\);\-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ \€"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,20 +256,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFE8B800"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FFE8B800"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="8"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
@@ -304,8 +347,47 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,6 +424,18 @@
         <bgColor rgb="FFF9F9F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -517,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -535,42 +629,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -582,7 +667,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -590,13 +675,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -604,50 +689,50 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="21" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -665,6 +750,45 @@
     <xf numFmtId="4" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="23" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -976,12 +1100,34 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CF73B0C2-0298-4E76-ACD4-FB2262E82E09}">
+  <we:reference id="11d7cf85-ae5a-43b8-bc58-1e1a151cce24" version="1.0.0.1" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;9f29c837-4c61-4b45-81e5-0c3847217a62&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -991,89 +1137,96 @@
     <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="57" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="34"/>
+    </row>
+    <row r="3" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17" t="s">
+      <c r="C5" s="17">
+        <v>46159</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="18" t="s">
+      <c r="F5" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19">
-        <v>46159</v>
-      </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="67">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22"/>
+      <c r="B7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="24" t="s">
+      <c r="C7" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="26"/>
-    </row>
-    <row r="8" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="23"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="21"/>
+    </row>
+    <row r="8" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1082,72 +1235,72 @@
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="29"/>
-    </row>
-    <row r="10" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="39" t="s">
+      <c r="B10" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="41" t="s">
-        <v>3</v>
+      <c r="F10" s="38" t="s">
+        <v>49</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="62">
+      <c r="B11" s="59">
         <v>1</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="68"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="65"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="66" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="64">
+      <c r="B14" s="61">
         <v>2</v>
       </c>
       <c r="C14" s="9"/>
@@ -1156,40 +1309,40 @@
       <c r="F14" s="9"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="65"/>
+      <c r="B15" s="62"/>
       <c r="C15" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" s="7">
-        <f>101*1.33665</f>
-        <v>135.00164999999998</v>
+        <f>101*1</f>
+        <v>101</v>
       </c>
       <c r="E15" s="8">
         <f>D15*B14</f>
-        <v>270.00329999999997</v>
-      </c>
-      <c r="F15" s="13">
-        <f>E15</f>
-        <v>270.00329999999997</v>
+        <v>202</v>
+      </c>
+      <c r="F15" s="11">
+        <f>E15*1.23</f>
+        <v>248.46</v>
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="64">
+      <c r="B17" s="61">
         <v>1</v>
       </c>
       <c r="C17" s="9"/>
@@ -1198,40 +1351,40 @@
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="65"/>
+      <c r="B18" s="62"/>
       <c r="C18" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" s="7">
-        <f>126*1.26985</f>
-        <v>160.00109999999998</v>
+        <f>126*1.254</f>
+        <v>158.00399999999999</v>
       </c>
       <c r="E18" s="8">
         <f>D18*B17</f>
-        <v>160.00109999999998</v>
-      </c>
-      <c r="F18" s="13">
-        <f>E18</f>
-        <v>160.00109999999998</v>
+        <v>158.00399999999999</v>
+      </c>
+      <c r="F18" s="11">
+        <f>E18*1.23</f>
+        <v>194.34491999999997</v>
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="30"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="27"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="27"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="64">
+      <c r="B20" s="61">
         <v>4</v>
       </c>
       <c r="C20" s="9"/>
@@ -1240,11 +1393,11 @@
       <c r="F20" s="9"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="65"/>
+      <c r="B21" s="62"/>
       <c r="C21" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21" s="7">
         <f>48.386556*1.291655</f>
@@ -1253,26 +1406,26 @@
       <c r="E21" s="8">
         <v>250</v>
       </c>
-      <c r="F21" s="13">
-        <f>E21</f>
-        <v>250</v>
+      <c r="F21" s="11">
+        <f>E21*1.23</f>
+        <v>307.5</v>
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="64">
+      <c r="B23" s="61">
         <v>1</v>
       </c>
       <c r="C23" s="9"/>
@@ -1281,11 +1434,11 @@
       <c r="F23" s="9"/>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="56" t="s">
-        <v>31</v>
+      <c r="B24" s="62"/>
+      <c r="C24" s="53" t="s">
+        <v>27</v>
       </c>
       <c r="D24" s="7">
         <v>90</v>
@@ -1294,56 +1447,91 @@
         <f>D24*B23</f>
         <v>90</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="11">
         <f>E24</f>
         <v>90</v>
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25">
+        <f>(622-102)*1.23</f>
+        <v>639.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="D26" s="11"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="61">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="7">
+        <v>20</v>
+      </c>
+      <c r="E27" s="8">
+        <f>D27*B26</f>
+        <v>20</v>
+      </c>
+      <c r="F27" s="11">
+        <f>E27</f>
+        <v>20</v>
+      </c>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="D28" s="11"/>
-      <c r="F28" s="12"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="86">
+        <f>F57-J25-30-15</f>
+        <v>185.70492000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="G33" s="2"/>
     </row>
@@ -1439,75 +1627,335 @@
       <c r="A56" s="1"/>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="42"/>
-      <c r="B58" s="43"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="44"/>
-      <c r="F58" s="45">
-        <f>SUM(F12,F15,F18,F24,F21)</f>
-        <v>770.00439999999992</v>
-      </c>
-      <c r="G58" s="46"/>
+    <row r="57" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="39"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="41"/>
+      <c r="F57" s="42">
+        <f>SUM(F15,F18,F21,F6,F24,F27)</f>
+        <v>870.30492000000004</v>
+      </c>
+      <c r="G57" s="43"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="1"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="59"/>
-      <c r="C60" s="59"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="59"/>
-      <c r="F60" s="59"/>
-      <c r="G60" s="60"/>
-    </row>
-    <row r="61" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="31"/>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="33"/>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="47"/>
-      <c r="B62" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="49"/>
-      <c r="D62" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="50"/>
+      <c r="A59" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="57"/>
+    </row>
+    <row r="60" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="28"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="30"/>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="44"/>
+      <c r="B61" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="46"/>
+      <c r="D61" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="D61:F61"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B26:B28"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EE36EBC-FF62-4F1F-90F1-D44BE4882F5B}">
+  <dimension ref="B2:G19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="B2" s="71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="72" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="73">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="75" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="76">
+        <f>'PROJETO DE AUDIO'!B11</f>
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <f>'PROJETO DE AUDIO'!C12&amp;" "&amp;'PROJETO DE AUDIO'!C13</f>
+        <v>Behringer Xenyx  X1832USB</v>
+      </c>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77">
+        <f>E7*$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="77">
+        <f>E7+F7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="76">
+        <f>'PROJETO DE AUDIO'!B14</f>
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <f>'PROJETO DE AUDIO'!C15&amp;" "&amp;'PROJETO DE AUDIO'!C16</f>
+        <v>Audibax Arkansas 8 Coluna ativa 2 vias 8" c/ Bluetooth, 80W RMS, XLR/RCA/1/8"</v>
+      </c>
+      <c r="D8" s="77">
+        <f>'PROJETO DE AUDIO'!D15</f>
+        <v>101</v>
+      </c>
+      <c r="E8" s="77">
+        <f>'PROJETO DE AUDIO'!E15</f>
+        <v>202</v>
+      </c>
+      <c r="F8" s="77">
+        <f>E8*$C$4</f>
+        <v>46.46</v>
+      </c>
+      <c r="G8" s="77">
+        <f>E8+F8</f>
+        <v>248.46</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="76">
+        <f>'PROJETO DE AUDIO'!B17</f>
+        <v>1</v>
+      </c>
+      <c r="C9" t="str">
+        <f>'PROJETO DE AUDIO'!C18&amp;" "&amp;'PROJETO DE AUDIO'!C19</f>
+        <v>Audibax MC XLR 164 30 Stage Box 30m — 16 ins / 4 outs</v>
+      </c>
+      <c r="D9" s="77">
+        <f>'PROJETO DE AUDIO'!D18</f>
+        <v>158.00399999999999</v>
+      </c>
+      <c r="E9" s="77">
+        <f>'PROJETO DE AUDIO'!E18</f>
+        <v>158.00399999999999</v>
+      </c>
+      <c r="F9" s="77">
+        <f>E9*$C$4</f>
+        <v>36.340919999999997</v>
+      </c>
+      <c r="G9" s="77">
+        <f>E9+F9</f>
+        <v>194.34492</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="76">
+        <f>'PROJETO DE AUDIO'!B20</f>
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <f>'PROJETO DE AUDIO'!C21&amp;" "&amp;'PROJETO DE AUDIO'!C22</f>
+        <v>Cabo XLR/XLR 50m 3-Pin XLR c/ fichas Amphenol</v>
+      </c>
+      <c r="D10" s="77">
+        <f>'PROJETO DE AUDIO'!D21</f>
+        <v>62.498736990179999</v>
+      </c>
+      <c r="E10" s="77">
+        <f>'PROJETO DE AUDIO'!E21</f>
+        <v>250</v>
+      </c>
+      <c r="F10" s="77">
+        <f>E10*$C$4</f>
+        <v>57.5</v>
+      </c>
+      <c r="G10" s="77">
+        <f>E10+F10</f>
+        <v>307.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="76">
+        <f>'PROJETO DE AUDIO'!B23</f>
+        <v>1</v>
+      </c>
+      <c r="C11" t="str">
+        <f>'PROJETO DE AUDIO'!C24&amp;" "&amp;'PROJETO DE AUDIO'!C25</f>
+        <v>Restauro e Reabilitação de Coluna Parte elétrica e estrutural</v>
+      </c>
+      <c r="D11" s="77">
+        <f>'PROJETO DE AUDIO'!D24</f>
+        <v>90</v>
+      </c>
+      <c r="E11" s="77">
+        <f>'PROJETO DE AUDIO'!E24</f>
+        <v>90</v>
+      </c>
+      <c r="F11" s="77">
+        <f>E11*$C$4</f>
+        <v>20.7</v>
+      </c>
+      <c r="G11" s="77">
+        <f>E11+F11</f>
+        <v>110.7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="76">
+        <f>'PROJETO DE AUDIO'!B26</f>
+        <v>1</v>
+      </c>
+      <c r="C12" t="str">
+        <f>'PROJETO DE AUDIO'!C27&amp;" "&amp;'PROJETO DE AUDIO'!C28</f>
+        <v>Acessórios de montagem Abraçadeiras de aluminio/plástico, Fita Fita Termo Retratil, etc.</v>
+      </c>
+      <c r="D12" s="77">
+        <f>'PROJETO DE AUDIO'!D27</f>
+        <v>20</v>
+      </c>
+      <c r="E12" s="77">
+        <f>'PROJETO DE AUDIO'!E27</f>
+        <v>20</v>
+      </c>
+      <c r="F12" s="77">
+        <f>E12*$C$4</f>
+        <v>4.6000000000000005</v>
+      </c>
+      <c r="G12" s="77">
+        <f>E12+F12</f>
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C13" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="77">
+        <f>'PROJETO DE AUDIO'!F6</f>
+        <v>10</v>
+      </c>
+      <c r="F13" s="77">
+        <f>E13*$C$4</f>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="G13" s="77">
+        <f>E13+F13</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C15" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81">
+        <f>SUM(E7:E13)</f>
+        <v>730.00400000000002</v>
+      </c>
+      <c r="F15" s="81">
+        <f>SUM(F7:F13)</f>
+        <v>167.90091999999999</v>
+      </c>
+      <c r="G15" s="82">
+        <f>SUM(G7:G13)</f>
+        <v>897.90492000000006</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="83">
+        <f>E15</f>
+        <v>730.00400000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="83">
+        <f>F15</f>
+        <v>167.90091999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B19" s="84" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="85">
+        <f>G15</f>
+        <v>897.90492000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>